--- a/partner_results/ncit/DigitRubberClassesWithDuplicateBaseLabels.xlsx
+++ b/partner_results/ncit/DigitRubberClassesWithDuplicateBaseLabels.xlsx
@@ -424,14 +424,14 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Pick one label</t>
+          <t>Pick one class (Decision to remove duplicates)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Multiple DIGITRUBBER classes use the same base label 'spectrum ' with different partner tags: 'spectrum [ifnano]', spectrum  [ncit], spectrum  [allotrope]</t>
+          <t>Multiple DIGITRUBBER classes use the same base label 'operator ' with different partner tags: 'operator [hsh]', operator  [ncit]</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
@@ -439,7 +439,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Multiple DIGITRUBBER classes use the same base label 'sample ' with different partner tags: 'sample [ifnano]', sample  [sosa], sample  [dik], sample  [nmrcv]</t>
+          <t>Multiple DIGITRUBBER classes use the same base label 'torque ' with different partner tags: 'torque [dik]', torque  [om]</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -447,7 +447,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Multiple DIGITRUBBER classes use the same base label 'sensor ' with different partner tags: 'sensor [chmo]', sensor  [sosa]</t>
+          <t>Multiple DIGITRUBBER classes use the same base label 'laser-induced breakdown spectroscopy ' with different partner tags: 'laser-induced breakdown spectroscopy [ifnano]', laser-induced breakdown spectroscopy  [chmo]</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -455,7 +455,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Multiple DIGITRUBBER classes use the same base label 'peak ' with different partner tags: 'peak [ifnano]', peak  [ncit], peak  [allotrope], peak  [ms]</t>
+          <t>Multiple DIGITRUBBER classes use the same base label 'quality of a substance ' with different partner tags: 'quality of a substance [dik]', quality of a substance  [pato]</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -463,7 +463,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Multiple DIGITRUBBER classes use the same base label 'organic group ' with different partner tags: 'organic group [dik]', organic group  [chebi]</t>
+          <t>Multiple DIGITRUBBER classes use the same base label 'standard deviation ' with different partner tags: 'standard deviation [Wikipedia]', standard deviation  [ncit], standard deviation  [ms], standard deviation  [allotrope], standard deviation  [ifnano]</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -471,7 +471,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Multiple DIGITRUBBER classes use the same base label 'filler ' with different partner tags: 'filler [dik]', filler  [Arlanxeo]</t>
+          <t>Multiple DIGITRUBBER classes use the same base label 'validation ' with different partner tags: 'validation [edam]', validation  [ncit], validation  [obi]</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -479,7 +479,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Multiple DIGITRUBBER classes use the same base label 'geometry ' with different partner tags: 'geometry [imr]', geometry  [geosparql]</t>
+          <t>Multiple DIGITRUBBER classes use the same base label 'stearic acid ' with different partner tags: 'stearic acid [dik]', stearic acid  [ncit]</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -487,7 +487,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Multiple DIGITRUBBER classes use the same base label 'stearic acid ' with different partner tags: 'stearic acid [dik]', stearic acid  [ncit]</t>
+          <t>Multiple DIGITRUBBER classes use the same base label 'quality of a liquid ' with different partner tags: 'quality of a liquid [dik]', quality of a liquid  [pato]</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -495,7 +495,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Multiple DIGITRUBBER classes use the same base label 'quality of a liquid ' with different partner tags: 'quality of a liquid [dik]', quality of a liquid  [pato]</t>
+          <t>Multiple DIGITRUBBER classes use the same base label 'supervisor ' with different partner tags: 'supervisor [hsh]', supervisor  [m4i], supervisor  [ncit]</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -503,7 +503,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Multiple DIGITRUBBER classes use the same base label 'supervisor ' with different partner tags: 'supervisor [hsh]', supervisor  [ncit], supervisor  [m4i]</t>
+          <t>Multiple DIGITRUBBER classes use the same base label 'Raman spectroscopy ' with different partner tags: 'Raman spectroscopy [ifnano]', Raman spectroscopy  [ncit]</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -511,7 +511,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Multiple DIGITRUBBER classes use the same base label 'optical quality ' with different partner tags: 'optical quality [dik]', optical quality  [pato]</t>
+          <t>Multiple DIGITRUBBER classes use the same base label 'organic group ' with different partner tags: 'organic group [dik]', organic group  [chebi]</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
@@ -519,7 +519,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Multiple DIGITRUBBER classes use the same base label 'organic divalent group ' with different partner tags: 'organic divalent group [dik]', organic divalent group  [chebi]</t>
+          <t>Multiple DIGITRUBBER classes use the same base label 'Mooney viscosity ' with different partner tags: 'Mooney viscosity [ifnano]', Mooney viscosity  [dik]</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
@@ -527,7 +527,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Multiple DIGITRUBBER classes use the same base label 'crosslink ' with different partner tags: 'crosslink [dik]', crosslink  [ncit]</t>
+          <t>Multiple DIGITRUBBER classes use the same base label 'monomer ' with different partner tags: 'monomer [ifnano]', monomer  [ncit]</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
@@ -535,7 +535,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Multiple DIGITRUBBER classes use the same base label 'dithiocarbamate ' with different partner tags: 'dithiocarbamate [dik]', dithiocarbamate  [chebi]</t>
+          <t>Multiple DIGITRUBBER classes use the same base label 'temperature ' with different partner tags: 'temperature [pato]', temperature  [ncit], temperature  [om], temperature  [efo]</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
@@ -543,7 +543,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Multiple DIGITRUBBER classes use the same base label 'agent ' with different partner tags: 'agent [ita]', agent  [ncit]</t>
+          <t>Multiple DIGITRUBBER classes use the same base label 'vulcanization ' with different partner tags: 'vulcanization [dik]', vulcanization  [Arlanxeo]</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
@@ -551,7 +551,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Multiple DIGITRUBBER classes use the same base label 'Raman spectroscopy ' with different partner tags: 'Raman spectroscopy [ifnano]', Raman spectroscopy  [ncit]</t>
+          <t>Multiple DIGITRUBBER classes use the same base label 'dithiocarbamate ' with different partner tags: 'dithiocarbamate [dik]', dithiocarbamate  [chebi]</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
@@ -559,7 +559,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Multiple DIGITRUBBER classes use the same base label 'organodiyl group ' with different partner tags: 'organodiyl group [dik]', organodiyl group  [chebi]</t>
+          <t>Multiple DIGITRUBBER classes use the same base label 'material processing ' with different partner tags: 'material processing [dik]', material processing  [obi]</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
@@ -575,7 +575,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Multiple DIGITRUBBER classes use the same base label 'temperature ' with different partner tags: 'temperature [pato]', temperature  [efo], temperature  [om], temperature  [ncit]</t>
+          <t>Multiple DIGITRUBBER classes use the same base label 'optical quality ' with different partner tags: 'optical quality [dik]', optical quality  [pato]</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
@@ -583,7 +583,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Multiple DIGITRUBBER classes use the same base label 'zinc ' with different partner tags: 'zinc [ifnano]', zinc  [efo], zinc  [ncit]</t>
+          <t>Multiple DIGITRUBBER classes use the same base label 'carbon black ' with different partner tags: 'carbon black [dik]', carbon black  [chebi], carbon black  [Arlanxeo]</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
@@ -591,7 +591,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Multiple DIGITRUBBER classes use the same base label 'concentration ' with different partner tags: 'concentration [ifnano]', concentration  [edam], concentration  [dik], concentration  [bwmd], concentration  [ecso], concentration  [ncit]</t>
+          <t>Multiple DIGITRUBBER classes use the same base label 'concentration ' with different partner tags: 'concentration [ifnano]', concentration  [bwmd], concentration  [ecso], concentration  [edam], concentration  [ncit], concentration  [dik]</t>
         </is>
       </c>
       <c r="B22" t="inlineStr"/>
@@ -599,7 +599,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Multiple DIGITRUBBER classes use the same base label 'quality of a substance ' with different partner tags: 'quality of a substance [dik]', quality of a substance  [pato]</t>
+          <t>Multiple DIGITRUBBER classes use the same base label 'function ' with different partner tags: 'function [dik]', function  [ncit]</t>
         </is>
       </c>
       <c r="B23" t="inlineStr"/>
@@ -607,7 +607,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Multiple DIGITRUBBER classes use the same base label 'group ' with different partner tags: 'group [dik]', group  [ncit], group  [chebi]</t>
+          <t>Multiple DIGITRUBBER classes use the same base label 'polymer ' with different partner tags: 'polymer [chebi]', polymer  [dik]</t>
         </is>
       </c>
       <c r="B24" t="inlineStr"/>
@@ -615,7 +615,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Multiple DIGITRUBBER classes use the same base label 'material processing ' with different partner tags: 'material processing [dik]', material processing  [obi]</t>
+          <t>Multiple DIGITRUBBER classes use the same base label 'synthetic rubber ' with different partner tags: 'synthetic rubber [hsh]', synthetic rubber  [dik]</t>
         </is>
       </c>
       <c r="B25" t="inlineStr"/>
@@ -623,7 +623,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Multiple DIGITRUBBER classes use the same base label 'polymer ' with different partner tags: 'polymer [chebi]', polymer  [dik]</t>
+          <t>Multiple DIGITRUBBER classes use the same base label 'processed material ' with different partner tags: 'processed material [dik]', processed material  [obi]</t>
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
@@ -631,7 +631,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Multiple DIGITRUBBER classes use the same base label 'monomer ' with different partner tags: 'monomer [ifnano]', monomer  [ncit]</t>
+          <t>Multiple DIGITRUBBER classes use the same base label 'agglomerate ' with different partner tags: 'agglomerate [dik]', agglomerate  [enm]</t>
         </is>
       </c>
       <c r="B27" t="inlineStr"/>
@@ -647,7 +647,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Multiple DIGITRUBBER classes use the same base label 'mixing ' with different partner tags: 'mixing [dik]', mixing  [chmo], mixing  [ncit]</t>
+          <t>Multiple DIGITRUBBER classes use the same base label 'sample ' with different partner tags: 'sample [ifnano]', sample  [dik], sample  [sosa], sample  [nmrcv]</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
@@ -655,7 +655,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Multiple DIGITRUBBER classes use the same base label 'validation ' with different partner tags: 'validation [edam]', validation  [obi], validation  [ncit]</t>
+          <t>Multiple DIGITRUBBER classes use the same base label 'group ' with different partner tags: 'group [dik]', group  [chebi], group  [ncit]</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
@@ -663,7 +663,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Multiple DIGITRUBBER classes use the same base label 'carbon black ' with different partner tags: 'carbon black [dik]', carbon black  [chebi], carbon black  [Arlanxeo]</t>
+          <t>Multiple DIGITRUBBER classes use the same base label 'geometry ' with different partner tags: 'geometry [imr]', geometry  [geosparql]</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
@@ -671,7 +671,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Multiple DIGITRUBBER classes use the same base label 'Mooney viscosity ' with different partner tags: 'Mooney viscosity [ifnano]', Mooney viscosity  [dik]</t>
+          <t>Multiple DIGITRUBBER classes use the same base label 'hydrocarbylene group ' with different partner tags: 'hydrocarbylene group [dik]', hydrocarbylene group  [chebi]</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
@@ -679,7 +679,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Multiple DIGITRUBBER classes use the same base label 'cost ' with different partner tags: 'cost [hsh]', cost  [ncit]</t>
+          <t>Multiple DIGITRUBBER classes use the same base label 'aggregate ' with different partner tags: 'aggregate [enm]', aggregate  [dik]</t>
         </is>
       </c>
       <c r="B33" t="inlineStr"/>
@@ -695,7 +695,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Multiple DIGITRUBBER classes use the same base label 'torque ' with different partner tags: 'torque [dik]', torque  [om]</t>
+          <t>Multiple DIGITRUBBER classes use the same base label 'mixing ' with different partner tags: 'mixing [dik]', mixing  [chmo], mixing  [ncit]</t>
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
@@ -703,7 +703,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Multiple DIGITRUBBER classes use the same base label 'vulcanization ' with different partner tags: 'vulcanization [dik]', vulcanization  [Arlanxeo]</t>
+          <t>Multiple DIGITRUBBER classes use the same base label 'photometry ' with different partner tags: 'photometry [ifnano]', photometry  [ncit]</t>
         </is>
       </c>
       <c r="B36" t="inlineStr"/>
@@ -711,7 +711,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Multiple DIGITRUBBER classes use the same base label 'hydrocarbylene group ' with different partner tags: 'hydrocarbylene group [dik]', hydrocarbylene group  [chebi]</t>
+          <t>Multiple DIGITRUBBER classes use the same base label 'peak ' with different partner tags: 'peak [ifnano]', peak  [ms], peak  [allotrope], peak  [ncit]</t>
         </is>
       </c>
       <c r="B37" t="inlineStr"/>
@@ -719,7 +719,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Multiple DIGITRUBBER classes use the same base label 'standard deviation ' with different partner tags: 'standard deviation [Wikipedia]', standard deviation  [allotrope], standard deviation  [ifnano], standard deviation  [ncit], standard deviation  [ms]</t>
+          <t>Multiple DIGITRUBBER classes use the same base label 'cost ' with different partner tags: 'cost [hsh]', cost  [ncit]</t>
         </is>
       </c>
       <c r="B38" t="inlineStr"/>
@@ -727,7 +727,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Multiple DIGITRUBBER classes use the same base label 'operator ' with different partner tags: 'operator [hsh]', operator  [ncit]</t>
+          <t>Multiple DIGITRUBBER classes use the same base label 'organic divalent group ' with different partner tags: 'organic divalent group [dik]', organic divalent group  [chebi]</t>
         </is>
       </c>
       <c r="B39" t="inlineStr"/>
@@ -735,7 +735,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Multiple DIGITRUBBER classes use the same base label 'function ' with different partner tags: 'function [dik]', function  [ncit]</t>
+          <t>Multiple DIGITRUBBER classes use the same base label 'organodiyl group ' with different partner tags: 'organodiyl group [dik]', organodiyl group  [chebi]</t>
         </is>
       </c>
       <c r="B40" t="inlineStr"/>
@@ -743,7 +743,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Multiple DIGITRUBBER classes use the same base label 'agglomerate ' with different partner tags: 'agglomerate [dik]', agglomerate  [enm]</t>
+          <t>Multiple DIGITRUBBER classes use the same base label 'spectrum ' with different partner tags: 'spectrum [ifnano]', spectrum  [allotrope], spectrum  [ncit]</t>
         </is>
       </c>
       <c r="B41" t="inlineStr"/>
@@ -751,7 +751,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Multiple DIGITRUBBER classes use the same base label 'synthetic rubber ' with different partner tags: 'synthetic rubber [hsh]', synthetic rubber  [dik]</t>
+          <t>Multiple DIGITRUBBER classes use the same base label 'natural rubber ' with different partner tags: 'natural rubber [hsh]', natural rubber  [ncit]</t>
         </is>
       </c>
       <c r="B42" t="inlineStr"/>
@@ -759,7 +759,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Multiple DIGITRUBBER classes use the same base label 'processed material ' with different partner tags: 'processed material [dik]', processed material  [obi]</t>
+          <t>Multiple DIGITRUBBER classes use the same base label 'sensor ' with different partner tags: 'sensor [chmo]', sensor  [sosa]</t>
         </is>
       </c>
       <c r="B43" t="inlineStr"/>
@@ -767,7 +767,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Multiple DIGITRUBBER classes use the same base label 'natural rubber ' with different partner tags: 'natural rubber [hsh]', natural rubber  [ncit]</t>
+          <t>Multiple DIGITRUBBER classes use the same base label 'zinc ' with different partner tags: 'zinc [ifnano]', zinc  [ncit], zinc  [efo]</t>
         </is>
       </c>
       <c r="B44" t="inlineStr"/>
@@ -775,7 +775,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Multiple DIGITRUBBER classes use the same base label 'aggregate ' with different partner tags: 'aggregate [enm]', aggregate  [dik]</t>
+          <t>Multiple DIGITRUBBER classes use the same base label 'agent ' with different partner tags: 'agent [ita]', agent  [ncit]</t>
         </is>
       </c>
       <c r="B45" t="inlineStr"/>
@@ -783,7 +783,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Multiple DIGITRUBBER classes use the same base label 'laser-induced breakdown spectroscopy ' with different partner tags: 'laser-induced breakdown spectroscopy [ifnano]', laser-induced breakdown spectroscopy  [chmo]</t>
+          <t>Multiple DIGITRUBBER classes use the same base label 'filler ' with different partner tags: 'filler [dik]', filler  [Arlanxeo]</t>
         </is>
       </c>
       <c r="B46" t="inlineStr"/>
@@ -791,7 +791,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Multiple DIGITRUBBER classes use the same base label 'photometry ' with different partner tags: 'photometry [ifnano]', photometry  [ncit]</t>
+          <t>Multiple DIGITRUBBER classes use the same base label 'crosslink ' with different partner tags: 'crosslink [dik]', crosslink  [ncit]</t>
         </is>
       </c>
       <c r="B47" t="inlineStr"/>
